--- a/site/exports/ustc-math.xlsx
+++ b/site/exports/ustc-math.xlsx
@@ -453,7 +453,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="65" customWidth="1" min="6" max="6"/>
     <col width="65" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="26.6" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
@@ -482,7 +482,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>核对日期</t>
+          <t>已记录来源检索日期</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -549,12 +549,12 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录；部分职业履历，学历与师承仍有缺项；历史985学校名录采样关联，非该校现职认定；已核现任单位：西安电子科技大学；现校官方简介明确目前任职；不据此断言是否另有兼任中科大。中科大旧名录仅作为采样和历史关联，不计其中科大现职人数。；https://faculty.xidian.edu.cn/BLJ/zh_CN/index.htm</t>
+          <t>分批核实资料，不是完整名录；部分职业履历，学历与师承仍有缺项；历史985学校名录采样关联，非该校现职认定；已核现任单位：西安电子科技大学；现校官方简介明确目前任职；不据此断言是否另有兼任中科大。中科大旧名录仅作为采样和历史关联，不计其中科大现职人数。；https://faculty.xidian.edu.cn/BLJ/zh_CN/index.htm；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
@@ -602,12 +602,12 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
@@ -655,12 +655,12 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
@@ -3568,7 +3568,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -3605,7 +3605,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">

--- a/site/exports/ustc-math.xlsx
+++ b/site/exports/ustc-math.xlsx
@@ -14,11 +14,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'导师'!$A$1:$L$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'论文'!$A$1:$L$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'导师'!$A$1:$L$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'论文'!$A$1:$L$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -453,8 +453,8 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="65" customWidth="1" min="6" max="6"/>
     <col width="65" customWidth="1" min="7" max="7"/>
-    <col width="26.6" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="40.59999999999999" customWidth="1" min="8" max="8"/>
+    <col width="23.8" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
@@ -477,7 +477,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>官方主页</t>
+          <t>个人主页／职业网站（来源类型见说明）</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -487,7 +487,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>缺项与冲突</t>
+          <t>来源说明与待核事项</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -502,7 +502,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>替代官方职业报道（非个人主页）</t>
+          <t>替代职业资料来源（非已核个人主页）</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -675,12 +675,66 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>陈世炳</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>校区未标注</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>数学科学学院</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.ustc.edu.cn/chenshibing/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>未知（来源日期异常）</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Necessary retained professional excerpts only, not original HTTP/full page; discrete field concatenation disclosed.；Directory and current employment unverified. Old raw roster was preflight identity inventory only, not newly certified directory.；Source-reported own doctoral-stage supervision retained; original thesis documents not checked, source does not explicitly use thesis-supervisor wording.；Publisher metadata/full texts not checked.；来源记载职业信息：职业职称：教授。上述为留存来源职业表述，不作本轮当前任职或资格认证；指导他人的资格不新增本人导师关系。</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>官方资料（原来源）；公开个人页（访问与内容时效见来源记录）</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>ustc</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>中国科学技术大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K4"/>
+  <autoFilter ref="A1:K5"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -692,13 +746,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S21"/>
+  <dimension ref="A1:S26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="29.4" customWidth="1" min="2" max="2"/>
     <col width="26.6" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="29.4" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
@@ -774,7 +828,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>确证授位</t>
+          <t>来源记载学位</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
@@ -2203,8 +2257,331 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>陈世炳</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>博士</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>University of Toronto</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr"/>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr"/>
+      <c r="I22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr"/>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源记载（学位获授日期）：2013</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr"/>
+      <c r="Q22" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.ustc.edu.cn/chenshibing/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>ustc</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>中国科学技术大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>陈世炳</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>学士</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>北京大学</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr"/>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr"/>
+      <c r="I23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源记载（学位获授日期）：2005</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr"/>
+      <c r="Q23" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.ustc.edu.cn/chenshibing/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>ustc</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>中国科学技术大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>陈世炳</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>硕士</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>北京大学</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr"/>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源记载（学位获授日期）：2008</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr"/>
+      <c r="Q24" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.ustc.edu.cn/chenshibing/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>ustc</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>中国科学技术大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>陈世炳</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>education_background</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>博士后</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>MSRI</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr"/>
+      <c r="I25" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr"/>
+      <c r="Q25" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.ustc.edu.cn/chenshibing/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>ustc</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>中国科学技术大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>陈世炳</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>education_background</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>博士后</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>MSI@ANU</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr"/>
+      <c r="I26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr"/>
+      <c r="Q26" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.ustc.edu.cn/chenshibing/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>ustc</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>中国科学技术大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S21"/>
+  <autoFilter ref="A1:S26"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q3" r:id="rId2"/>
@@ -2226,6 +2603,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q20" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q26" r:id="rId25"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2237,14 +2619,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="18.2" customWidth="1" min="2" max="2"/>
+    <col width="54.59999999999999" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="49" customWidth="1" min="5" max="5"/>
+    <col width="65" customWidth="1" min="5" max="5"/>
     <col width="33.59999999999999" customWidth="1" min="6" max="6"/>
     <col width="65" customWidth="1" min="7" max="7"/>
     <col width="65" customWidth="1" min="8" max="8"/>
@@ -2498,8 +2880,58 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>陈世炳</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Robert McCann</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>source_reported_doctoral_degree_advisor</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>博士</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>来源记载的关系；本轮未进行学位论文原件及导师当前人事认证。；原关系与阶段自述保留；未知不表示关系不存在，不建立现职身份导航。</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.ustc.edu.cn/chenshibing/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>ustc</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>中国科学技术大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L4"/>
+  <autoFilter ref="A1:L5"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId2"/>
@@ -2509,6 +2941,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I4" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J4" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2520,7 +2953,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2771,8 +3204,102 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>陈世炳</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Regularity of singular set in optimal transportation</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr"/>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.ustc.edu.cn/chenshibing/zh_CN/lwcg/274860/list/index.htm</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.ustc.edu.cn/chenshibing/zh_CN/lwcg/274860/list/index.htm</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；source_attributed_recovery_not_reverified</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；来源authors_as_source：Shibing Chen、Jiakun Liu；来源person_contribution_role_as_source：列名作者；来源书目信息（publication_status_as_source）：Accepted by Inventiones</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>ustc</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>中国科学技术大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>陈世炳</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Global regularity for the Monge-Ampère equation with natural boundary condition</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D6" s="2" t="inlineStr"/>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.ustc.edu.cn/chenshibing/zh_CN/lwcg/274860/list/index.htm</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr"/>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.ustc.edu.cn/chenshibing/zh_CN/lwcg/274860/list/index.htm</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；source_attributed_recovery_not_reverified</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；来源authors_as_source：陈世炳、Liu, Jiakun、Wang, Xu-Jia；来源person_contribution_role_as_source：列名作者；来源书目信息（卷）：194；来源书目信息（期）：3</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>ustc</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>中国科学技术大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L4"/>
+  <autoFilter ref="A1:L6"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
@@ -2782,6 +3309,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2793,14 +3324,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="50.4" customWidth="1" min="2" max="2"/>
+    <col width="65" customWidth="1" min="2" max="2"/>
     <col width="65" customWidth="1" min="3" max="3"/>
     <col width="65" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
@@ -3548,27 +4079,27 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>曹培根</t>
+          <t>陈世炳</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>institution-classification-9</t>
+          <t>new-recovery-ustc-chenshibing-s001-e88e986b3806</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</t>
+          <t>https://faculty.ustc.edu.cn/chenshibing/zh_CN/index.htm</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>历史985院校分类参考；非个人授位或就读当年建设身份的证明</t>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>未单独记录</t>
+          <t>2026-10-25T05:45:08Z</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -3585,42 +4116,116 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>陈世炳</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-ustc-chenshibing-s002-8cc2ca6705b0</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.ustc.edu.cn/chenshibing/zh_CN/lwcg/274860/list/index.htm</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T05:45:14Z</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>ustc</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>中国科学技术大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>曹培根</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>institution-classification-9</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>历史985院校分类参考；非个人授位或就读当年建设身份的证明</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>未单独记录</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>ustc</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>中国科学技术大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
           <t>陈卿</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>institution-classification-4</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>历史985院校分类参考；非个人授位或就读当年建设身份的证明</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>未单独记录</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>ustc</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>ustc</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>中国科学技术大学</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G22"/>
+  <autoFilter ref="A1:G24"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
@@ -3643,6 +4248,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId23"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/exports/ustc-math.xlsx
+++ b/site/exports/ustc-math.xlsx
@@ -2353,7 +2353,7 @@
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L23" s="2" t="b">
@@ -2416,7 +2416,7 @@
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L24" s="2" t="b">
